--- a/Project/outputs/tables/table_spillover_train.xlsx
+++ b/Project/outputs/tables/table_spillover_train.xlsx
@@ -436,19 +436,19 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>STOXX600</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>CAC40</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>FTSE100</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DAX</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Nikkei</t>
@@ -456,17 +456,17 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>HangSeng</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>CSI300</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>MSCI_EM</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -482,133 +482,133 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33.77</v>
+        <v>39.75</v>
       </c>
       <c r="C2" t="n">
-        <v>13.41</v>
+        <v>13.99</v>
       </c>
       <c r="D2" t="n">
-        <v>12.67</v>
+        <v>14.59</v>
       </c>
       <c r="E2" t="n">
-        <v>10.49</v>
+        <v>16.66</v>
       </c>
       <c r="F2" t="n">
-        <v>3.93</v>
+        <v>4.59</v>
       </c>
       <c r="G2" t="n">
-        <v>3.56</v>
+        <v>5.85</v>
       </c>
       <c r="H2" t="n">
-        <v>0.74</v>
+        <v>4.42</v>
       </c>
       <c r="I2" t="n">
-        <v>21.43</v>
+        <v>0.15</v>
       </c>
       <c r="J2" t="n">
-        <v>11.9</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>STOXX600</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.72</v>
+        <v>14.63</v>
       </c>
       <c r="C3" t="n">
-        <v>24.17</v>
+        <v>26.84</v>
       </c>
       <c r="D3" t="n">
-        <v>19.33</v>
+        <v>21.98</v>
       </c>
       <c r="E3" t="n">
-        <v>17.61</v>
+        <v>18.89</v>
       </c>
       <c r="F3" t="n">
-        <v>4.83</v>
+        <v>5.8</v>
       </c>
       <c r="G3" t="n">
-        <v>4.44</v>
+        <v>5.32</v>
       </c>
       <c r="H3" t="n">
-        <v>1.44</v>
+        <v>6.13</v>
       </c>
       <c r="I3" t="n">
-        <v>12.46</v>
+        <v>0.41</v>
       </c>
       <c r="J3" t="n">
-        <v>11.12</v>
+        <v>10.73</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>FTSE100</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.01</v>
+        <v>14.83</v>
       </c>
       <c r="C4" t="n">
-        <v>20.82</v>
+        <v>21.22</v>
       </c>
       <c r="D4" t="n">
-        <v>24.08</v>
+        <v>28.44</v>
       </c>
       <c r="E4" t="n">
-        <v>15.26</v>
+        <v>22.31</v>
       </c>
       <c r="F4" t="n">
-        <v>4.5</v>
+        <v>4.37</v>
       </c>
       <c r="G4" t="n">
-        <v>4.58</v>
+        <v>3.65</v>
       </c>
       <c r="H4" t="n">
-        <v>1.27</v>
+        <v>4.55</v>
       </c>
       <c r="I4" t="n">
-        <v>13.48</v>
+        <v>0.64</v>
       </c>
       <c r="J4" t="n">
-        <v>10.38</v>
+        <v>10.98</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>FTSE100</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.13</v>
+        <v>15.89</v>
       </c>
       <c r="C5" t="n">
-        <v>19.03</v>
+        <v>17.34</v>
       </c>
       <c r="D5" t="n">
-        <v>15.8</v>
+        <v>21.7</v>
       </c>
       <c r="E5" t="n">
-        <v>22.59</v>
+        <v>31.58</v>
       </c>
       <c r="F5" t="n">
-        <v>6.47</v>
+        <v>4.47</v>
       </c>
       <c r="G5" t="n">
-        <v>6.67</v>
+        <v>4.12</v>
       </c>
       <c r="H5" t="n">
-        <v>1.35</v>
+        <v>4.4</v>
       </c>
       <c r="I5" t="n">
-        <v>12.96</v>
+        <v>0.51</v>
       </c>
       <c r="J5" t="n">
-        <v>10.01</v>
+        <v>11.12</v>
       </c>
     </row>
     <row r="6">
@@ -618,133 +618,133 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.66</v>
+        <v>12.72</v>
       </c>
       <c r="C6" t="n">
-        <v>12.06</v>
+        <v>10.15</v>
       </c>
       <c r="D6" t="n">
-        <v>10.36</v>
+        <v>9.23</v>
       </c>
       <c r="E6" t="n">
-        <v>10.91</v>
+        <v>10.22</v>
       </c>
       <c r="F6" t="n">
-        <v>30.43</v>
+        <v>35.4</v>
       </c>
       <c r="G6" t="n">
-        <v>11.87</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>0.41</v>
+        <v>12.53</v>
       </c>
       <c r="I6" t="n">
-        <v>11.3</v>
+        <v>0.14</v>
       </c>
       <c r="J6" t="n">
-        <v>4.46</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>HangSeng</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11.18</v>
+        <v>10.62</v>
       </c>
       <c r="C7" t="n">
-        <v>8.880000000000001</v>
+        <v>10.39</v>
       </c>
       <c r="D7" t="n">
-        <v>9.92</v>
+        <v>10.03</v>
       </c>
       <c r="E7" t="n">
-        <v>11.06</v>
+        <v>10.09</v>
       </c>
       <c r="F7" t="n">
-        <v>9.869999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="G7" t="n">
-        <v>29.77</v>
+        <v>34.9</v>
       </c>
       <c r="H7" t="n">
-        <v>4.9</v>
+        <v>14.22</v>
       </c>
       <c r="I7" t="n">
-        <v>14.41</v>
+        <v>0.24</v>
       </c>
       <c r="J7" t="n">
-        <v>6.28</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>CSI300</t>
+          <t>HangSeng</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.01</v>
+        <v>11.16</v>
       </c>
       <c r="C8" t="n">
-        <v>2.76</v>
+        <v>10.79</v>
       </c>
       <c r="D8" t="n">
-        <v>2.45</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>4.7</v>
+        <v>9.98</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5600000000000001</v>
+        <v>10.31</v>
       </c>
       <c r="G8" t="n">
-        <v>12.27</v>
+        <v>13.47</v>
       </c>
       <c r="H8" t="n">
-        <v>71.93000000000001</v>
+        <v>32.78</v>
       </c>
       <c r="I8" t="n">
-        <v>3.33</v>
+        <v>2.47</v>
       </c>
       <c r="J8" t="n">
-        <v>1.35</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>MSCI_EM</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22.46</v>
+        <v>0.57</v>
       </c>
       <c r="C9" t="n">
-        <v>12.03</v>
+        <v>1.96</v>
       </c>
       <c r="D9" t="n">
-        <v>12.54</v>
+        <v>1.25</v>
       </c>
       <c r="E9" t="n">
-        <v>10.06</v>
+        <v>0.85</v>
       </c>
       <c r="F9" t="n">
-        <v>5.5</v>
+        <v>0.15</v>
       </c>
       <c r="G9" t="n">
-        <v>6.87</v>
+        <v>0.86</v>
       </c>
       <c r="H9" t="n">
-        <v>0.73</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>29.81</v>
+        <v>86.16</v>
       </c>
       <c r="J9" t="n">
-        <v>11.17</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="10">
@@ -754,31 +754,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8.279999999999999</v>
+        <v>7.53</v>
       </c>
       <c r="C10" t="n">
-        <v>9.48</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>9.49</v>
+        <v>8.94</v>
       </c>
       <c r="E10" t="n">
-        <v>9.68</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>8.699999999999999</v>
+        <v>8.08</v>
       </c>
       <c r="G10" t="n">
-        <v>8.779999999999999</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>3.51</v>
+        <v>8.4</v>
       </c>
       <c r="I10" t="n">
-        <v>8.77</v>
+        <v>1.73</v>
       </c>
       <c r="J10" t="n">
-        <v>66.68000000000001</v>
+        <v>60.52</v>
       </c>
     </row>
   </sheetData>
